--- a/mech_elec_ai_calculator/outputs/工程量清单.xlsx
+++ b/mech_elec_ai_calculator/outputs/工程量清单.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K10"/>
+  <dimension ref="A1:K11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -511,13 +511,13 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G2" t="n">
         <v>5000</v>
       </c>
       <c r="H2" t="n">
-        <v>20000</v>
+        <v>10000</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -537,12 +537,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>DL004</t>
+          <t>DL003</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>开关</t>
+          <t>配电箱</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
@@ -552,13 +552,13 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G3" t="n">
-        <v>50</v>
+        <v>800</v>
       </c>
       <c r="H3" t="n">
-        <v>150</v>
+        <v>1600</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -567,7 +567,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>switch</t>
+          <t>distribution_box</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
@@ -578,37 +578,37 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>DL101</t>
+          <t>DL004</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Unknown电缆</t>
+          <t>开关</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>米</t>
+          <t>个</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>3061.53</v>
+        <v>3</v>
       </c>
       <c r="G4" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="H4" t="n">
-        <v>306153</v>
+        <v>150</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>线缆</t>
+          <t>设备</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>power</t>
+          <t>switch</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
@@ -619,12 +619,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>DL201</t>
+          <t>DL101</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>桥架</t>
+          <t>电力电缆(桥架敷设)</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -634,21 +634,29 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>11200</v>
+        <v>12505.2</v>
       </c>
       <c r="G5" t="n">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="H5" t="n">
-        <v>3360000</v>
+        <v>1250520</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>桥架</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
+          <t>线缆</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>cable_tray</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>基础长度: 12500.00m, 预留: 5.20m, 敷设方式: 桥架</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -656,32 +664,32 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>DL401</t>
+          <t>DL201</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>电缆头</t>
+          <t>电缆桥架</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>个</t>
+          <t>米</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2</v>
+        <v>11200</v>
       </c>
       <c r="G6" t="n">
-        <v>50</v>
+        <v>300</v>
       </c>
       <c r="H6" t="n">
-        <v>100</v>
+        <v>3360000</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>辅材</t>
+          <t>桥架</t>
         </is>
       </c>
       <c r="J6" t="inlineStr"/>
@@ -693,12 +701,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>DL402</t>
+          <t>DL401</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>接线端子</t>
+          <t>电缆头</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -708,13 +716,13 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>28</v>
+        <v>2</v>
       </c>
       <c r="G7" t="n">
-        <v>5</v>
+        <v>50</v>
       </c>
       <c r="H7" t="n">
-        <v>140</v>
+        <v>100</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -725,34 +733,71 @@
       <c r="K7" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>合计</t>
-        </is>
+      <c r="A8" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>DL402</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>接线端子</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr"/>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>个</t>
+        </is>
+      </c>
+      <c r="F8" t="n">
+        <v>28</v>
+      </c>
+      <c r="G8" t="n">
+        <v>5</v>
       </c>
       <c r="H8" t="n">
-        <v>3686543</v>
-      </c>
+        <v>140</v>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>辅材</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>项目名称</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Electrical Project</t>
-        </is>
+          <t>合计</t>
+        </is>
+      </c>
+      <c r="H9" t="n">
+        <v>4622510</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
+          <t>项目名称</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Electrical Project</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
           <t>项目编号</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B11" t="inlineStr">
         <is>
           <t>EP-001</t>
         </is>

--- a/mech_elec_ai_calculator/outputs/工程量清单.xlsx
+++ b/mech_elec_ai_calculator/outputs/工程量清单.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K11"/>
+  <dimension ref="A1:K15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -511,13 +511,13 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="G2" t="n">
         <v>5000</v>
       </c>
       <c r="H2" t="n">
-        <v>10000</v>
+        <v>30000</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -537,12 +537,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>DL003</t>
+          <t>DL002</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>配电箱</t>
+          <t>电气设备</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
@@ -552,13 +552,13 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G3" t="n">
-        <v>800</v>
+        <v>2000</v>
       </c>
       <c r="H3" t="n">
-        <v>1600</v>
+        <v>10000</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -567,7 +567,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>distribution_box</t>
+          <t>equipment</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
@@ -578,12 +578,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>DL004</t>
+          <t>DL003</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>开关</t>
+          <t>配电箱</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
@@ -596,10 +596,10 @@
         <v>3</v>
       </c>
       <c r="G4" t="n">
-        <v>50</v>
+        <v>800</v>
       </c>
       <c r="H4" t="n">
-        <v>150</v>
+        <v>2400</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -608,7 +608,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>switch</t>
+          <t>distribution_box</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
@@ -619,44 +619,40 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>DL101</t>
+          <t>DL004</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>电力电缆(桥架敷设)</t>
+          <t>开关</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>米</t>
+          <t>个</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>12505.2</v>
+        <v>4</v>
       </c>
       <c r="G5" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="H5" t="n">
-        <v>1250520</v>
+        <v>200</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>线缆</t>
+          <t>设备</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>cable_tray</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>基础长度: 12500.00m, 预留: 5.20m, 敷设方式: 桥架</t>
-        </is>
-      </c>
+          <t>switch</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -664,35 +660,39 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>DL201</t>
+          <t>DL005</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>电缆桥架</t>
+          <t>插座</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>米</t>
+          <t>个</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>11200</v>
+        <v>4</v>
       </c>
       <c r="G6" t="n">
-        <v>300</v>
+        <v>20</v>
       </c>
       <c r="H6" t="n">
-        <v>3360000</v>
+        <v>80</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>桥架</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr"/>
+          <t>设备</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>socket</t>
+        </is>
+      </c>
       <c r="K6" t="inlineStr"/>
     </row>
     <row r="7">
@@ -701,12 +701,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>DL401</t>
+          <t>DL006</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>电缆头</t>
+          <t>照明灯具</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -716,20 +716,24 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G7" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="H7" t="n">
-        <v>100</v>
+        <v>400</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>辅材</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr"/>
+          <t>设备</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>lighting</t>
+        </is>
+      </c>
       <c r="K7" t="inlineStr"/>
     </row>
     <row r="8">
@@ -738,70 +742,226 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>DL402</t>
+          <t>DL101</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>接线端子</t>
+          <t>电力电缆(桥架敷设)</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
+          <t>米</t>
+        </is>
+      </c>
+      <c r="F8" t="n">
+        <v>72312</v>
+      </c>
+      <c r="G8" t="n">
+        <v>100</v>
+      </c>
+      <c r="H8" t="n">
+        <v>7231200</v>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>线缆</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>cable_tray</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>基础长度: 72300.00m, 预留: 12.00m, 敷设方式: 桥架</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>DL102</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>控制电缆(桥架敷设)</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr"/>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>米</t>
+        </is>
+      </c>
+      <c r="F9" t="n">
+        <v>11012</v>
+      </c>
+      <c r="G9" t="n">
+        <v>50</v>
+      </c>
+      <c r="H9" t="n">
+        <v>550600</v>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>线缆</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>cable_tray</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>基础长度: 11000.00m, 预留: 12.00m, 敷设方式: 桥架</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>DL201</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>电缆桥架</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr"/>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>米</t>
+        </is>
+      </c>
+      <c r="F10" t="n">
+        <v>19300</v>
+      </c>
+      <c r="G10" t="n">
+        <v>300</v>
+      </c>
+      <c r="H10" t="n">
+        <v>5790000</v>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>桥架</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>DL401</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>电缆头</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr"/>
+      <c r="E11" t="inlineStr">
+        <is>
           <t>个</t>
         </is>
       </c>
-      <c r="F8" t="n">
-        <v>28</v>
-      </c>
-      <c r="G8" t="n">
+      <c r="F11" t="n">
+        <v>4</v>
+      </c>
+      <c r="G11" t="n">
+        <v>50</v>
+      </c>
+      <c r="H11" t="n">
+        <v>200</v>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>辅材</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>DL402</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>接线端子</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>个</t>
+        </is>
+      </c>
+      <c r="F12" t="n">
+        <v>104</v>
+      </c>
+      <c r="G12" t="n">
         <v>5</v>
       </c>
-      <c r="H8" t="n">
-        <v>140</v>
-      </c>
-      <c r="I8" t="inlineStr">
+      <c r="H12" t="n">
+        <v>520</v>
+      </c>
+      <c r="I12" t="inlineStr">
         <is>
           <t>辅材</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
         <is>
           <t>合计</t>
         </is>
       </c>
-      <c r="H9" t="n">
-        <v>4622510</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
+      <c r="H13" t="n">
+        <v>13615600</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
         <is>
           <t>项目名称</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Electrical Project</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
+      <c r="B14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
         <is>
           <t>项目编号</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>EP-001</t>
-        </is>
-      </c>
+      <c r="B15" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
